--- a/reports/jobs_2026-10-04.xlsx
+++ b/reports/jobs_2026-10-04.xlsx
@@ -4184,7 +4184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4212,35 +4212,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>INDmoney</t>
+          <t>Cuemath</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.indmoney.com/careers</t>
+          <t>https://www.cuemath.com/careers/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.indmoney.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cuemath</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.cuemath.com/careers/</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4249,18 +4229,18 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Log9 Materials</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>https://www.log9materials.com/careers</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4269,18 +4249,18 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Signzy</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.signzy.com/careers/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4289,18 +4269,18 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Vymo</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>https://getvymo.com/careers/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4309,18 +4289,18 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Ather Energy</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4329,18 +4309,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4349,18 +4329,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4369,18 +4349,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4389,18 +4369,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4409,18 +4389,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4429,18 +4409,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Darwinbox</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://darwinbox.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4449,18 +4429,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4469,18 +4449,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4489,38 +4469,18 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Pocket FM</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://pocketfm.com/careers</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://pocketfm.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4529,18 +4489,18 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4549,38 +4509,18 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Zoom India</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://careers.zoom.us/</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_CONNECTION_RESET at https://careers.zoom.us/
-Call log:
-  - navigating to "https://careers.zoom.us/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4589,26 +4529,6 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cigniti Technologies</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://www.cigniti.com/careers/</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.cigniti.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
